--- a/Config/Language.xlsx
+++ b/Config/Language.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37E2E4F-0349-47D9-9F05-F4D436DF7987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4EFF3-FD06-4916-8407-E1946EB85E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6490" yWindow="8490" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="128">
   <si>
     <t>#</t>
   </si>
@@ -409,6 +409,94 @@
   </si>
   <si>
     <t>Language</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>斧头描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>子弹描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Axes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命比例护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDecs_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>Attr_ATK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前血量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attr_Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大血量</t>
+  </si>
+  <si>
+    <t>当前蓝量</t>
+  </si>
+  <si>
+    <t>Attr_Power</t>
+  </si>
+  <si>
+    <t>最大蓝量</t>
+  </si>
+  <si>
+    <t>Attr_MaxPower</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>Attr_HuDun</t>
+  </si>
+  <si>
+    <t>护盾增益</t>
+  </si>
+  <si>
+    <t>Attr_HuDunBoost</t>
+  </si>
+  <si>
+    <t>技能急速</t>
+  </si>
+  <si>
+    <t>Attr_CooldownReduce</t>
+  </si>
+  <si>
+    <t>掏出一把斧头,朝最近的敌人挥砍，造成 {0} = [20 + 100%Attr_ATK] 伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朝最近的敌人扔出子弹壳，造成 {0} = [ 100%Attr_ATK] 伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attr_MaxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给自己生成 {0} = [ 10%Attr_MaxHp] 的护盾，持续4秒，不可叠加</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -749,7 +837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1060,233 +1148,387 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>36</v>
+      <c r="B19">
+        <v>5001</v>
+      </c>
+      <c r="C19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B20">
-        <v>10001</v>
+        <v>5002</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="2">
-        <v>10002</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>14</v>
+      <c r="B21">
+        <v>5003</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>26</v>
+        <v>115</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B22">
-        <v>10003</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>15</v>
+        <v>5004</v>
+      </c>
+      <c r="C22" t="s">
+        <v>116</v>
       </c>
       <c r="D22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>25</v>
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="2">
-        <v>10004</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>16</v>
+      <c r="B23">
+        <v>5005</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" t="s">
-        <v>27</v>
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B24">
-        <v>10005</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>17</v>
+        <v>5006</v>
+      </c>
+      <c r="C24" t="s">
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" t="s">
-        <v>28</v>
+        <v>121</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="2">
-        <v>10006</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>18</v>
+      <c r="B25">
+        <v>5007</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>29</v>
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B26">
-        <v>10007</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>19</v>
+        <v>5008</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" t="s">
-        <v>30</v>
+        <v>110</v>
+      </c>
+      <c r="E26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="E27" s="2"/>
+        <v>36</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="2">
-        <v>11001</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>20</v>
+      <c r="B28">
+        <v>10001</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
-        <v>11002</v>
+        <v>10002</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>32</v>
+        <v>14</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="2">
-        <v>11003</v>
+      <c r="B30">
+        <v>10003</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F30" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="B31" s="2">
+        <v>10004</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="2">
-        <v>12001</v>
+      <c r="B32">
+        <v>10005</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>10007</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B36" s="2">
+        <v>11001</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B37" s="2">
+        <v>11002</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B38" s="2">
+        <v>11003</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B40" s="2">
+        <v>12001</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
         <v>12002</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D41" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F41" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>106</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
+        <v>20002</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" t="s">
+        <v>105</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B45" s="2">
+        <v>20003</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Language.xlsx
+++ b/Config/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDF4EFF3-FD06-4916-8407-E1946EB85E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC72B494-BED6-49AA-9B44-AF39E1ACE2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="164">
   <si>
     <t>#</t>
   </si>
@@ -83,10 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>匕首</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>护甲板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -169,9 +165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ItemName_Dagger</t>
-  </si>
-  <si>
     <t>ItemName_ArmorPlate</t>
   </si>
   <si>
@@ -420,22 +413,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ItemDecs_Bullet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDecs_Axes</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>生命比例护盾</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ItemDecs_Shield</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击力</t>
   </si>
   <si>
@@ -497,6 +478,170 @@
   </si>
   <si>
     <t>给自己生成 {0} = [ 10%Attr_MaxHp] 的护盾，持续4秒，不可叠加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命护盾</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗狂热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_MoreFast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗狂热描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Axes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Bullet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_ArmorPlate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_MoreFast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_FlySword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_FlySword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次主动技能释放后增加释放者 20 点技能急速，持续5s，最多叠加10层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在身后生成6把飞剑，朝最近的敌人突刺，每把造成 {0} = [ 100%Attr_ATK]伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_FlySwordAnim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemName_FlySwordAnim</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续飞剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_WhirlingAxe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成两把斧头围绕自身旋转，对周围目标造成 {0} = [ 100%Attr_ATK]伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemDesc_ThornArmor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加 20 点 护盾增益,增加500最大生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回主界面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Confirm_ReturnTitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将返回主界面，为保存的游戏进度将丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次受到伤害，给伤害来源 {0} = [5 + 1%Attr_MaxHp] 伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每隔0.2s生成一把飞剑，随机选取攻击距离内的目标，并对飞行途中的敌人造成 {0} = [ 100%Attr_ATK]伤害，在释放结束时朝人群最密集的区域释放爆炸。造成 {0} = [ 100%Attr_ATK]伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能类型_主动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType_Active</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType_Auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SkillType_Passive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartBattle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameFinish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏通关，将回到主界面。\n 感谢游玩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -837,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -863,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -917,7 +1062,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -931,13 +1076,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
@@ -948,16 +1093,16 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>56</v>
-      </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -965,16 +1110,16 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
         <v>60</v>
-      </c>
-      <c r="D8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,16 +1127,16 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -999,16 +1144,16 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
         <v>67</v>
       </c>
-      <c r="D10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" t="s">
-        <v>69</v>
-      </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1016,16 +1161,16 @@
         <v>15</v>
       </c>
       <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" t="s">
         <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,16 +1178,16 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
         <v>74</v>
       </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>76</v>
-      </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1050,16 +1195,16 @@
         <v>17</v>
       </c>
       <c r="C13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
         <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1067,16 +1212,16 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1084,16 +1229,16 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1101,434 +1246,647 @@
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>21</v>
       </c>
       <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
         <v>95</v>
       </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>22</v>
       </c>
       <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
         <v>99</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>100</v>
       </c>
-      <c r="E18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" t="s">
+        <v>162</v>
+      </c>
+      <c r="E21" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22">
         <v>5001</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>5002</v>
+      </c>
+      <c r="C23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>5003</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>5004</v>
+      </c>
+      <c r="C25" t="s">
         <v>111</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D25" t="s">
         <v>112</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E25" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B20">
-        <v>5002</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>5005</v>
+      </c>
+      <c r="C26" t="s">
         <v>113</v>
       </c>
-      <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>5003</v>
-      </c>
-      <c r="C21" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>5006</v>
+      </c>
+      <c r="C27" t="s">
         <v>115</v>
       </c>
-      <c r="E21" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>5004</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D27" t="s">
         <v>116</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>5007</v>
+      </c>
+      <c r="C28" t="s">
         <v>117</v>
       </c>
-      <c r="E22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>5005</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="D28" t="s">
         <v>118</v>
       </c>
-      <c r="D23" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B24">
-        <v>5006</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B25">
-        <v>5007</v>
-      </c>
-      <c r="C25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B26">
+      <c r="E28" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29">
         <v>5008</v>
       </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28">
-        <v>10001</v>
-      </c>
-      <c r="C28" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="2">
-        <v>10002</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>14</v>
+      <c r="C29" t="s">
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="E29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30">
-        <v>10003</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>15</v>
+        <v>5010</v>
+      </c>
+      <c r="C30" t="s">
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="2">
-        <v>10004</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>16</v>
+        <v>153</v>
+      </c>
+      <c r="E30" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>5011</v>
+      </c>
+      <c r="C31" t="s">
+        <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+      <c r="E31" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32">
-        <v>10005</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>17</v>
+        <v>5012</v>
+      </c>
+      <c r="C32" t="s">
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" t="s">
-        <v>28</v>
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B33" s="2">
-        <v>10006</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" t="s">
-        <v>29</v>
+      <c r="A33" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>10007</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>19</v>
+        <v>10001</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="B35" s="2">
+        <v>10002</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B36" s="2">
-        <v>11001</v>
+      <c r="B36">
+        <v>10003</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
-        <v>11002</v>
+        <v>10004</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B38" s="2">
-        <v>11003</v>
+      <c r="B38">
+        <v>10005</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F38" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="B39" s="2">
+        <v>10006</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="2">
-        <v>12001</v>
+      <c r="B40">
+        <v>10007</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
-        <v>12002</v>
+        <v>10008</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>126</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>49</v>
+      <c r="B42">
+        <v>10009</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
-        <v>20001</v>
+        <v>10010</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B44" s="2">
-        <v>20002</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="E44" s="2"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
+        <v>11001</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="2">
+        <v>11002</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="2">
+        <v>11003</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B49" s="2">
+        <v>12001</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B50" s="2">
+        <v>12002</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="2">
+        <v>20002</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B54" s="2">
         <v>20003</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="C54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D54" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B55" s="2">
+        <v>20004</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>131</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B56" s="2">
+        <v>20008</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>127</v>
+      </c>
+      <c r="D56" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
+        <v>20009</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D57" t="s">
+        <v>136</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="2">
+        <v>20010</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D58" t="s">
+        <v>140</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="2">
+        <v>21001</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>143</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B60" s="2">
+        <v>21002</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Language.xlsx
+++ b/Config/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\zizouqi\Config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D8A900-DD23-4819-8D27-52ABEC6E6768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54382D86-CF90-4C3B-B4A8-15DA548E5672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21720" yWindow="-3600" windowWidth="21840" windowHeight="37920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="238">
   <si>
     <t>#</t>
   </si>
@@ -854,6 +854,46 @@
   </si>
   <si>
     <t>Choose Reward</t>
+  </si>
+  <si>
+    <t>独占全屏</t>
+  </si>
+  <si>
+    <t>无边框全屏</t>
+  </si>
+  <si>
+    <t>最大化窗口</t>
+  </si>
+  <si>
+    <t>窗口模式</t>
+  </si>
+  <si>
+    <t>FullScreenMode_ExclusiveFullScreen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullScreenMode_FullScreenWindow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullScreenMode_MaximizedWindow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullScreenMode_Windowed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExclusiveFullScreen</t>
+  </si>
+  <si>
+    <t>FullScreenWindow</t>
+  </si>
+  <si>
+    <t>MaximizedWindow</t>
+  </si>
+  <si>
+    <t>Windowed</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -1743,426 +1783,432 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B33">
-        <v>5001</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="E33" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="F33" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B34">
-        <v>5002</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>231</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>227</v>
       </c>
       <c r="F34" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B35">
-        <v>5003</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>228</v>
       </c>
       <c r="F35" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B36">
-        <v>5004</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>233</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>229</v>
       </c>
       <c r="F36" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B37">
-        <v>5005</v>
+        <v>5001</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B38">
-        <v>5006</v>
+        <v>5002</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B39">
-        <v>5007</v>
+        <v>5003</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B40">
-        <v>5008</v>
+        <v>5004</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F40" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B41">
-        <v>5010</v>
+        <v>5005</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="F41" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B42">
-        <v>5011</v>
+        <v>5006</v>
       </c>
       <c r="C42" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="F42" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B43">
-        <v>5012</v>
+        <v>5007</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="D43" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="E43" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="F43" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>28</v>
+      <c r="B44">
+        <v>5008</v>
+      </c>
+      <c r="C44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B45">
-        <v>10001</v>
+        <v>5010</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="2">
-        <v>10002</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>13</v>
+      <c r="B46">
+        <v>5011</v>
+      </c>
+      <c r="C46" t="s">
+        <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>172</v>
+        <v>148</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B47">
-        <v>10003</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>96</v>
+        <v>5012</v>
+      </c>
+      <c r="C47" t="s">
+        <v>145</v>
       </c>
       <c r="D47" t="s">
-        <v>116</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>117</v>
+        <v>149</v>
+      </c>
+      <c r="E47" t="s">
+        <v>151</v>
       </c>
       <c r="F47" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="2">
-        <v>10004</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F48" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B49">
-        <v>10005</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>15</v>
+        <v>10001</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>15</v>
+        <v>29</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
-        <v>10006</v>
+        <v>10002</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" t="s">
-        <v>174</v>
+        <v>13</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B51">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="D51" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
-        <v>10008</v>
+        <v>10004</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>119</v>
+        <v>31</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B53">
-        <v>10009</v>
+        <v>10005</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>128</v>
+        <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
-        <v>10010</v>
+        <v>10006</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="F54" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="E55" s="2"/>
+      <c r="B55">
+        <v>10007</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
-        <v>11001</v>
+        <v>10008</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="F56" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B57" s="2">
-        <v>11002</v>
+      <c r="B57">
+        <v>10009</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="D57" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="F57" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>42</v>
-      </c>
       <c r="B58" s="2">
-        <v>11003</v>
+        <v>10010</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="D58" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2175,193 +2221,255 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
-        <v>12001</v>
+        <v>11001</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
-        <v>12002</v>
+        <v>11002</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="B62" s="2">
+        <v>11003</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B63" s="2">
-        <v>20001</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" t="s">
-        <v>121</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F63" t="s">
-        <v>181</v>
-      </c>
+      <c r="A63" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
+        <v>12001</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D64" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F64" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B65" s="2">
+        <v>12002</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D65" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B67" s="2">
+        <v>20001</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" t="s">
+        <v>121</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F67" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B68" s="2">
         <v>20002</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D68" t="s">
         <v>122</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F68" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B65" s="2">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B69" s="2">
         <v>20003</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D69" t="s">
         <v>123</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F69" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B66" s="2">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B70" s="2">
         <v>20004</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D70" t="s">
         <v>124</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F70" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B67" s="2">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B71" s="2">
         <v>20008</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D71" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F71" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B68" s="2">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B72" s="2">
         <v>20009</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D72" t="s">
         <v>129</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="F68" t="s">
+      <c r="F72" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B69" s="2">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B73" s="2">
         <v>20010</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D73" t="s">
         <v>133</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F69" t="s">
+      <c r="F73" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B70" s="2">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B74" s="2">
         <v>21001</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D74" t="s">
         <v>136</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F74" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B71" s="2">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B75" s="2">
         <v>21002</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D75" t="s">
         <v>138</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F71" t="s">
+      <c r="F75" t="s">
         <v>189</v>
       </c>
     </row>
